--- a/artfynd/A 35824-2026 artfynd.xlsx
+++ b/artfynd/A 35824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136349072</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35824-2026 artfynd.xlsx
+++ b/artfynd/A 35824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136349072</v>
       </c>
       <c r="B2" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35824-2026 artfynd.xlsx
+++ b/artfynd/A 35824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136349072</v>
       </c>
       <c r="B2" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
